--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8e0463e98507465a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f8662bb7be54ac8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6f8662bb7be54ac8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc1346a1e1aee44ef"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc1346a1e1aee44ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5e000e4817f41b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc5e000e4817f41b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39863a80ae7c4a3b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R39863a80ae7c4a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf0a0a99863d473a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbf0a0a99863d473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22b73cf0a3b64c89"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R22b73cf0a3b64c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R555a88f7ce9642a4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R555a88f7ce9642a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0ea8d323ec8c405b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0ea8d323ec8c405b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86097bb611cc437f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R86097bb611cc437f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0bd484ebf4db475f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0bd484ebf4db475f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49992399543549b3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49992399543549b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89664f8f56a54d80"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89664f8f56a54d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb859c89b379545a2"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
+++ b/tests/Kookerella.CsOpenXmlDsl.Tests/Examples/AutoFilter/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb859c89b379545a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb34d2c13b794f99"/>
   </x:sheets>
 </x:workbook>
 </file>
